--- a/data/trans_bre/P19C08-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P19C08-Provincia-trans_bre.xlsx
@@ -660,17 +660,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,98; 2,53</t>
+          <t>-1,99; 2,06</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,1; 1,96</t>
+          <t>-1,47; 1,64</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,65; 0,0</t>
+          <t>-2,56; 0,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -765,17 +765,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,41</t>
+          <t>0,0; 1,61</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,87; 0,0</t>
+          <t>-1,6; 0,0</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,17</t>
+          <t>0,0; 0,19</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,98</t>
+          <t>0,0; 2,13</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,34; 1,1</t>
+          <t>-2,08; 1,14</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 2,0</t>
+          <t>-0,55; 2,33</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,93</t>
+          <t>0,0; 0,95</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 367,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,11; 0,0</t>
+          <t>-1,81; 0,0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-3,4; 0,27</t>
+          <t>-4,26; 0,27</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1075,7 +1075,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 1,4</t>
+          <t>-0,9; 1,41</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,0</t>
+          <t>0,0; 2,91</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,35; 5,01</t>
+          <t>-0,0; 4,46</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-2,78; 0,53</t>
+          <t>-2,33; 0,53</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1260,22 +1260,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,21; 1,21</t>
+          <t>-0,25; 1,21</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,74; 0,3</t>
+          <t>-1,68; 0,28</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,06</t>
+          <t>0,21; 2,17</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,42; 0,54</t>
+          <t>-2,78; 0,5</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-92,0; 124,61</t>
+          <t>-93,52; 105,99</t>
         </is>
       </c>
     </row>
@@ -1360,12 +1360,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 1,39</t>
+          <t>-0,75; 1,38</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 0,5</t>
+          <t>-1,11; 0,44</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1375,17 +1375,17 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 0,93</t>
+          <t>-0,67; 0,97</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-77,53; 664,84</t>
+          <t>-80,46; 585,39</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -1395,7 +1395,7 @@
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-66,5; 356,81</t>
+          <t>-71,48; 480,51</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,15; 0,58</t>
+          <t>-0,16; 0,57</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 0,39</t>
+          <t>-0,46; 0,37</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,16; 0,29</t>
+          <t>-0,15; 0,3</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 0,23</t>
+          <t>-0,5; 0,23</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-35,53; 294,33</t>
+          <t>-37,19; 318,01</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-52,14; 98,65</t>
+          <t>-53,59; 89,82</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-84,06; 583,59</t>
+          <t>-83,28; 704,03</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-64,0; 93,55</t>
+          <t>-66,69; 84,01</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P19C08-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P19C08-Provincia-trans_bre.xlsx
@@ -660,17 +660,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,99; 2,06</t>
+          <t>-1,99; 2,08</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,47; 1,64</t>
+          <t>-1,19; 1,7</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,56; 0,0</t>
+          <t>-2,55; 0,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,03</t>
+          <t>0,16</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -765,17 +765,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,61</t>
+          <t>0,0; 1,54</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,6; 0,0</t>
+          <t>-1,93; 0,0</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,19</t>
+          <t>0,0; 0,84</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,13</t>
+          <t>0,0; 1,94</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,08; 1,14</t>
+          <t>-2,31; 1,11</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 2,33</t>
+          <t>-0,48; 2,03</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,95</t>
+          <t>0,0; 0,85</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,81; 0,0</t>
+          <t>-2,22; 0,0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-4,26; 0,27</t>
+          <t>-4,17; 0,27</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>43,38%</t>
+          <t>45,27%</t>
         </is>
       </c>
     </row>
@@ -1060,7 +1060,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 2,14</t>
+          <t>-1,62; 2,17</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1075,7 +1075,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 1,41</t>
+          <t>-0,84; 1,29</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-0,31</t>
+          <t>-0,27</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>-53,44%</t>
+          <t>-51,42%</t>
         </is>
       </c>
     </row>
@@ -1160,12 +1160,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,91</t>
+          <t>0,0; 3,47</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-0,0; 4,46</t>
+          <t>0,32; 4,79</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-2,33; 0,53</t>
+          <t>-2,13; 0,5</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-0,55</t>
+          <t>-0,48</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>-44,02%</t>
+          <t>-34,16%</t>
         </is>
       </c>
     </row>
@@ -1260,22 +1260,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,25; 1,21</t>
+          <t>-0,38; 1,17</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,68; 0,28</t>
+          <t>-2,0; 0,27</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,21; 2,17</t>
+          <t>0,2; 2,17</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,78; 0,5</t>
+          <t>-2,31; 0,62</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-93,52; 105,99</t>
+          <t>-83,19; 126,7</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0,1</t>
+          <t>-0,09</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>18,51%</t>
+          <t>-12,36%</t>
         </is>
       </c>
     </row>
@@ -1360,12 +1360,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 1,38</t>
+          <t>-0,73; 1,43</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 0,44</t>
+          <t>-1,12; 0,43</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1375,17 +1375,17 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 0,97</t>
+          <t>-0,92; 0,64</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-80,46; 585,39</t>
+          <t>-74,62; 646,53</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 367,64</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -1395,7 +1395,7 @@
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-71,48; 480,51</t>
+          <t>-75,87; 214,71</t>
         </is>
       </c>
     </row>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>-0,07</t>
+          <t>-0,09</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>-15,38%</t>
+          <t>-16,26%</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,16; 0,57</t>
+          <t>-0,13; 0,58</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 0,37</t>
+          <t>-0,45; 0,42</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,15; 0,3</t>
+          <t>-0,17; 0,33</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 0,23</t>
+          <t>-0,49; 0,22</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-37,19; 318,01</t>
+          <t>-35,19; 304,49</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-53,59; 89,82</t>
+          <t>-52,5; 103,84</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-83,28; 704,03</t>
+          <t>-72,0; 772,94</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-66,69; 84,01</t>
+          <t>-60,89; 70,59</t>
         </is>
       </c>
     </row>
